--- a/bot/shablon.xlsx
+++ b/bot/shablon.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29630"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfatech.uz\Documents\nakladnoy_printer\bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72535112-B269-4958-B795-5FB4EDB11DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA35636-2C90-42CE-AC9B-AB001F034BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,7 +86,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -99,6 +99,15 @@
       <sz val="8"/>
       <color rgb="FF0C0C0C"/>
       <name val="sans-serif"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -146,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -159,6 +168,9 @@
     </xf>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -492,84 +504,85 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="21" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:7" ht="22.5">
       <c r="A9" s="1" t="s">
